--- a/projetos/fachada-sao-camilo/orcamento/Composicao_Custos_INTERNO_Sao_Camilo.xlsx
+++ b/projetos/fachada-sao-camilo/orcamento/Composicao_Custos_INTERNO_Sao_Camilo.xlsx
@@ -101,7 +101,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -497,7 +497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>COMPOSIÇÃO DE CUSTOS INTERNA – Fachada São Camilo (NÃO ENVIAR AO CLIENTE)</t>
+          <t>COMPOSIÇÃO DE CUSTOS INTERNA – Fachada São Camilo (NÃO ENVIAR AO CLIENTE) – BDI calculado para total de venda R$ 5.670.000,00</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.3</v>
+        <v>1.617815550655423</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
